--- a/astro-site/public/dl/bar-checklist-templates/BONUS-02-bar-events-calendar.xlsx
+++ b/astro-site/public/dl/bar-checklist-templates/BONUS-02-bar-events-calendar.xlsx
@@ -232,11 +232,11 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
       <protection locked="0" hidden="0"/>
     </xf>
@@ -956,17 +956,17 @@
       </c>
       <c r="B9" s="26" t="inlineStr">
         <is>
-          <t>Late May</t>
+          <t>May 5</t>
         </is>
       </c>
       <c r="C9" s="27" t="inlineStr">
         <is>
-          <t>Memorial Day weekend (last Mon of May)</t>
+          <t>Cinco de Mayo</t>
         </is>
       </c>
       <c r="D9" s="28" t="inlineStr">
         <is>
-          <t>Holiday hours, patio at full capacity and stock for several days in a row</t>
+          <t>Margaritas, mezcal, tequila, Mexican decorations</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="F9" s="29" t="inlineStr">
         <is>
-          <t>A long weekend moves more than a normal Saturday and is ordered with the same lead time</t>
+          <t>Already one of the biggest bar nights of the year in the US</t>
         </is>
       </c>
     </row>
@@ -988,17 +988,17 @@
       </c>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t>May 5</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>Cinco de Mayo</t>
+          <t>Late May</t>
+        </is>
+      </c>
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Memorial Day weekend (last Mon of May)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t>Margaritas, mezcal, tequila, Mexican decorations</t>
+          <t>Holiday hours, patio at full capacity and stock for several days in a row</t>
         </is>
       </c>
       <c r="E10" s="20" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Already one of the biggest bar nights of the year in the US</t>
+          <t>A long weekend moves more than a normal Saturday and is ordered with the same lead time</t>
         </is>
       </c>
     </row>
@@ -1215,7 +1215,7 @@
           <t>December</t>
         </is>
       </c>
-      <c r="C17" s="30" t="inlineStr">
+      <c r="C17" s="31" t="inlineStr">
         <is>
           <t>Holiday parties (company)</t>
         </is>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>The after-dinner drink with the family is a short, very profitable peak</t>
+          <t>Usually a short night: staff lean and post the hours early</t>
         </is>
       </c>
     </row>
@@ -1311,7 +1311,7 @@
           <t>Varies</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Local festivals &amp; street fairs</t>
         </is>
@@ -1340,12 +1340,12 @@
       </c>
       <c r="B21" s="26" t="inlineStr">
         <is>
-          <t>Varies</t>
-        </is>
-      </c>
-      <c r="C21" s="30" t="inlineStr">
-        <is>
-          <t>Big games &amp; sports nights</t>
+          <t>Feb (2nd Sun) · varies</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Super Bowl Sunday &amp; big games</t>
         </is>
       </c>
       <c r="D21" s="28" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="F21" s="29" t="inlineStr">
         <is>
-          <t>Super Bowl, March Madness, playoffs (NBA, NHL), World Series</t>
+          <t>Super Bowl on the 2nd Sunday in Feb; also March Madness, NBA/NHL playoffs, World Series</t>
         </is>
       </c>
     </row>
